--- a/Employee_Reports_wi52/Jonel Catibog Katigbak Q0561.xlsx
+++ b/Employee_Reports_wi52/Jonel Catibog Katigbak Q0561.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>555</v>
+        <v>547</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>610</v>
+        <v>602</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>610</v>
+        <v>602</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -970,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>615</v>
+        <v>607</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1068,11 +1068,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>615</v>
+        <v>607</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1117,11 +1117,11 @@
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1166,11 +1166,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>615</v>
+        <v>607</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1215,11 +1215,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>616</v>
+        <v>608</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1264,11 +1264,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1301,11 +1301,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>532</v>
+        <v>524</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1350,11 +1350,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1400,11 +1400,11 @@
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1449,11 +1449,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1486,11 +1486,11 @@
         </is>
       </c>
       <c r="H22" s="3" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -1535,11 +1535,11 @@
         </is>
       </c>
       <c r="H23" s="5" t="n">
-        <v>-182</v>
+        <v>-190</v>
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
@@ -1584,11 +1584,11 @@
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1633,11 +1633,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1670,11 +1670,11 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -1707,11 +1707,11 @@
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -1756,11 +1756,11 @@
         </is>
       </c>
       <c r="H28" s="3" t="n">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
@@ -1771,41 +1771,41 @@
       <c r="K28" s="3" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="n">
+      <c r="A29" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>IS0 55001 (Other Trainings)</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr"/>
-      <c r="D29" s="4" t="inlineStr"/>
-      <c r="E29" s="4" t="inlineStr"/>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>25-Aug-2024</t>
-        </is>
-      </c>
-      <c r="G29" s="4" t="inlineStr">
-        <is>
-          <t>25-Aug-2026</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="I29" s="4" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>EXPIRING SOON</t>
-        </is>
-      </c>
-      <c r="K29" s="4" t="inlineStr"/>
+      <c r="C29" s="3" t="inlineStr"/>
+      <c r="D29" s="3" t="inlineStr"/>
+      <c r="E29" s="3" t="inlineStr"/>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>26-Aug-2026</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>25-Aug-2028</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>728</v>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
@@ -1830,11 +1830,11 @@
         </is>
       </c>
       <c r="H30" s="3" t="n">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
@@ -2292,7 +2292,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7911</v>
+        <v>7903</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7901</v>
+        <v>7893</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2416,7 +2416,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7901</v>
+        <v>7893</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7901</v>
+        <v>7893</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7947</v>
+        <v>7939</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7947</v>
+        <v>7939</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7947</v>
+        <v>7939</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7947</v>
+        <v>7939</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7947</v>
+        <v>7939</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>7951</v>
+        <v>7943</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>7951</v>
+        <v>7943</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>7951</v>
+        <v>7943</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>7951</v>
+        <v>7943</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7951</v>
+        <v>7943</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
